--- a/2024-09-20018D Source Data Fig. 2.xlsx
+++ b/2024-09-20018D Source Data Fig. 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ytian\Desktop\Source Data_Clean_KNIT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1711A12-36EB-4F8A-BAAA-BD210691A11F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F13DFF7-7520-4C1C-9AE9-50ADF25C1736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8609,7 +8609,7 @@
         <v>32.75</v>
       </c>
       <c r="F9" s="15">
-        <v>39.6</v>
+        <v>39.74</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
@@ -13109,10 +13109,10 @@
         <v>92.7</v>
       </c>
       <c r="E3" s="15">
+        <v>1.75</v>
+      </c>
+      <c r="F3" s="15">
         <v>0.47</v>
-      </c>
-      <c r="F3" s="15">
-        <v>1.75</v>
       </c>
       <c r="G3" s="15">
         <v>3.19</v>
@@ -13148,7 +13148,6 @@
         <v>0.93</v>
       </c>
       <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>

--- a/2024-09-20018D Source Data Fig. 2.xlsx
+++ b/2024-09-20018D Source Data Fig. 2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ytian\Desktop\Source Data_Clean_KNIT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ytian\Desktop\To be revised\Source data\Clean version\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F13DFF7-7520-4C1C-9AE9-50ADF25C1736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CFFF43E-233A-469E-8501-214B88FDA8A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fig. 2b" sheetId="10" r:id="rId1"/>
@@ -3836,13 +3836,13 @@
         <v>6</v>
       </c>
       <c r="B3" s="15">
-        <v>98.5</v>
+        <v>98.52</v>
       </c>
       <c r="C3" s="15">
-        <v>99.8</v>
+        <v>99.84</v>
       </c>
       <c r="D3" s="15">
-        <v>99.8</v>
+        <v>99.78</v>
       </c>
       <c r="E3" s="15">
         <v>1.23</v>
@@ -3866,13 +3866,13 @@
         <v>7</v>
       </c>
       <c r="B4" s="15">
-        <v>99.2</v>
+        <v>99.23</v>
       </c>
       <c r="C4" s="15">
-        <v>97.8</v>
+        <v>97.77</v>
       </c>
       <c r="D4" s="15">
-        <v>99.2</v>
+        <v>99.15</v>
       </c>
       <c r="E4" s="15">
         <v>1.65</v>
@@ -5486,13 +5486,13 @@
         <v>1.59</v>
       </c>
       <c r="E7" s="15">
-        <v>99.5</v>
+        <v>99.53</v>
       </c>
       <c r="F7" s="15">
-        <v>99.7</v>
+        <v>99.73</v>
       </c>
       <c r="G7" s="15">
-        <v>99.7</v>
+        <v>99.65</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
